--- a/Team-Data/2007-08/3-22-2007-08.xlsx
+++ b/Team-Data/2007-08/3-22-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>0.435</v>
+        <v>0.426</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -688,10 +755,10 @@
         <v>4.4</v>
       </c>
       <c r="M2" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O2" t="n">
         <v>21</v>
@@ -706,16 +773,16 @@
         <v>12.4</v>
       </c>
       <c r="S2" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T2" t="n">
         <v>42.4</v>
       </c>
       <c r="U2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V2" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
         <v>7.4</v>
@@ -727,19 +794,19 @@
         <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB2" t="n">
         <v>96.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -760,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
         <v>27</v>
@@ -781,19 +848,19 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" t="n">
         <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.797</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L3" t="n">
         <v>7.2</v>
@@ -873,13 +940,13 @@
         <v>18.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O3" t="n">
         <v>20.7</v>
       </c>
       <c r="P3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q3" t="n">
         <v>0.77</v>
@@ -897,31 +964,31 @@
         <v>22.2</v>
       </c>
       <c r="V3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA3" t="n">
         <v>22.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,13 +1003,13 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL3" t="n">
         <v>10</v>
@@ -954,13 +1021,13 @@
         <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
@@ -978,13 +1045,13 @@
         <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>0.362</v>
+        <v>0.353</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,19 +1110,19 @@
         <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.445</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O4" t="n">
         <v>18.1</v>
@@ -1064,16 +1131,16 @@
         <v>25.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.71</v>
+        <v>0.708</v>
       </c>
       <c r="R4" t="n">
         <v>11.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T4" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U4" t="n">
         <v>20.9</v>
@@ -1091,7 +1158,7 @@
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
@@ -1100,10 +1167,10 @@
         <v>95.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.9</v>
+        <v>-5.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1121,7 +1188,7 @@
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
         <v>23</v>
@@ -1148,7 +1215,7 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>24</v>
@@ -1172,13 +1239,13 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
         <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.391</v>
+        <v>0.397</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1228,16 +1295,16 @@
         <v>84.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O5" t="n">
         <v>18.6</v>
@@ -1255,19 +1322,19 @@
         <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W5" t="n">
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
         <v>5.8</v>
@@ -1279,19 +1346,19 @@
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
@@ -1330,19 +1397,19 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>9</v>
@@ -1357,7 +1424,7 @@
         <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
         <v>7.1</v>
@@ -1419,28 +1486,28 @@
         <v>19.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R6" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V6" t="n">
         <v>14.1</v>
@@ -1464,7 +1531,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
@@ -1488,7 +1555,7 @@
         <v>12</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
@@ -1506,31 +1573,31 @@
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV6" t="n">
         <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1676,13 +1743,13 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN7" t="n">
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
@@ -1694,7 +1761,7 @@
         <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>7</v>
@@ -1703,7 +1770,7 @@
         <v>21</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW7" t="n">
         <v>29</v>
@@ -1712,7 +1779,7 @@
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
         <v>22</v>
@@ -1721,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1873,10 +1940,10 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>4</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,13 +2095,13 @@
         <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2055,13 +2122,13 @@
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
         <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
@@ -2079,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2240,10 +2307,10 @@
         <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
@@ -2261,7 +2328,7 @@
         <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA10" t="n">
         <v>12</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="n">
         <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.671</v>
+        <v>0.681</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J11" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="K11" t="n">
         <v>0.45</v>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N11" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O11" t="n">
         <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0.721</v>
@@ -2344,16 +2411,16 @@
         <v>12.1</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="T11" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V11" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
@@ -2365,16 +2432,16 @@
         <v>4.5</v>
       </c>
       <c r="Z11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>19.6</v>
       </c>
-      <c r="AA11" t="n">
-        <v>19.7</v>
-      </c>
       <c r="AB11" t="n">
-        <v>96.8</v>
+        <v>96.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD11" t="n">
         <v>4</v>
@@ -2383,19 +2450,19 @@
         <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>14</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>13</v>
       </c>
       <c r="AK11" t="n">
         <v>18</v>
@@ -2416,19 +2483,19 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
@@ -2440,7 +2507,7 @@
         <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>4</v>
@@ -2449,10 +2516,10 @@
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
         <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.414</v>
+        <v>0.406</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2505,13 +2572,13 @@
         <v>0.442</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M12" t="n">
         <v>24.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O12" t="n">
         <v>18.9</v>
@@ -2538,7 +2605,7 @@
         <v>15.2</v>
       </c>
       <c r="W12" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
         <v>5</v>
@@ -2547,7 +2614,7 @@
         <v>5.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA12" t="n">
         <v>21.7</v>
@@ -2556,19 +2623,19 @@
         <v>103.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
         <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
@@ -2592,7 +2659,7 @@
         <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP12" t="n">
         <v>18</v>
@@ -2601,7 +2668,7 @@
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>0.304</v>
+        <v>0.309</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,7 +2748,7 @@
         <v>34.4</v>
       </c>
       <c r="J13" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0.438</v>
@@ -2690,19 +2757,19 @@
         <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R13" t="n">
         <v>9.5</v>
@@ -2714,10 +2781,10 @@
         <v>39.9</v>
       </c>
       <c r="U13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2726,22 +2793,22 @@
         <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2759,10 +2826,10 @@
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>28</v>
@@ -2774,28 +2841,28 @@
         <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
@@ -2804,7 +2871,7 @@
         <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2953,7 +3020,7 @@
         <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
         <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J15" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L15" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M15" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O15" t="n">
         <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R15" t="n">
         <v>10.4</v>
@@ -3081,7 +3148,7 @@
         <v>19.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
         <v>6.1</v>
@@ -3099,13 +3166,13 @@
         <v>22.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3123,13 +3190,13 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3138,16 +3205,16 @@
         <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>12</v>
@@ -3162,13 +3229,13 @@
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>0.174</v>
+        <v>0.176</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3230,7 +3297,7 @@
         <v>77.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L16" t="n">
         <v>5.4</v>
@@ -3239,13 +3306,13 @@
         <v>15.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
         <v>17.1</v>
       </c>
       <c r="P16" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q16" t="n">
         <v>0.72</v>
@@ -3260,13 +3327,13 @@
         <v>37.9</v>
       </c>
       <c r="U16" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V16" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W16" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X16" t="n">
         <v>4.2</v>
@@ -3275,19 +3342,19 @@
         <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>92.8</v>
+        <v>93</v>
       </c>
       <c r="AC16" t="n">
-        <v>-8.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>0.353</v>
+        <v>0.343</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J17" t="n">
         <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L17" t="n">
         <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O17" t="n">
         <v>17.6</v>
@@ -3433,16 +3500,16 @@
         <v>0.736</v>
       </c>
       <c r="R17" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T17" t="n">
         <v>41</v>
       </c>
       <c r="U17" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
         <v>14.4</v>
@@ -3457,19 +3524,19 @@
         <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3502,7 +3569,7 @@
         <v>26</v>
       </c>
       <c r="AO17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP17" t="n">
         <v>21</v>
@@ -3517,13 +3584,13 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>23</v>
@@ -3538,13 +3605,13 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
         <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>0.261</v>
+        <v>0.25</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
@@ -3606,52 +3673,52 @@
         <v>0.343</v>
       </c>
       <c r="O18" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.732</v>
+        <v>0.73</v>
       </c>
       <c r="R18" t="n">
         <v>11.8</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V18" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W18" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X18" t="n">
         <v>3.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.5</v>
+        <v>-6.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3663,7 +3730,7 @@
         <v>27</v>
       </c>
       <c r="AH18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
         <v>12</v>
@@ -3672,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,22 +3757,22 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
         <v>19</v>
       </c>
       <c r="AU18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
         <v>12</v>
@@ -3717,7 +3784,7 @@
         <v>29</v>
       </c>
       <c r="AZ18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
         <v>30</v>
@@ -3726,7 +3793,7 @@
         <v>28</v>
       </c>
       <c r="BC18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" t="n">
         <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>0.414</v>
+        <v>0.42</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J19" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L19" t="n">
         <v>5.8</v>
@@ -3785,7 +3852,7 @@
         <v>16.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
         <v>20.2</v>
@@ -3794,10 +3861,10 @@
         <v>27.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R19" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S19" t="n">
         <v>30.8</v>
@@ -3812,7 +3879,7 @@
         <v>15.2</v>
       </c>
       <c r="W19" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X19" t="n">
         <v>4.7</v>
@@ -3827,7 +3894,7 @@
         <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC19" t="n">
         <v>-5.2</v>
@@ -3836,7 +3903,7 @@
         <v>4</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>20</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3854,16 +3921,16 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3872,25 +3939,25 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS19" t="n">
         <v>14</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW19" t="n">
         <v>25</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3908,7 +3975,7 @@
         <v>27</v>
       </c>
       <c r="BC19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,37 +4022,37 @@
         <v>38.5</v>
       </c>
       <c r="J20" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.463</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
         <v>19.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.39</v>
+        <v>0.389</v>
       </c>
       <c r="O20" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P20" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="T20" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
@@ -3994,7 +4061,7 @@
         <v>12.2</v>
       </c>
       <c r="W20" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>3.9</v>
@@ -4006,19 +4073,19 @@
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="AC20" t="n">
         <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
         <v>3</v>
@@ -4051,22 +4118,22 @@
         <v>29</v>
       </c>
       <c r="AP20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS20" t="n">
         <v>13</v>
       </c>
-      <c r="AS20" t="n">
-        <v>14</v>
-      </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.275</v>
+        <v>0.279</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4137,7 +4204,7 @@
         <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K21" t="n">
         <v>0.438</v>
@@ -4146,16 +4213,16 @@
         <v>5.8</v>
       </c>
       <c r="M21" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O21" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q21" t="n">
         <v>0.726</v>
@@ -4164,16 +4231,16 @@
         <v>12.1</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U21" t="n">
         <v>18.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
         <v>6.2</v>
@@ -4188,16 +4255,16 @@
         <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4218,10 +4285,10 @@
         <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>16</v>
@@ -4230,19 +4297,19 @@
         <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
         <v>25</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AT21" t="n">
         <v>16</v>
@@ -4266,13 +4333,13 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB21" t="n">
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22" t="n">
         <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>0.639</v>
+        <v>0.648</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4322,25 +4389,25 @@
         <v>78.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L22" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>0.386</v>
       </c>
       <c r="O22" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="P22" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.726</v>
+        <v>0.728</v>
       </c>
       <c r="R22" t="n">
         <v>9.5</v>
@@ -4349,7 +4416,7 @@
         <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U22" t="n">
         <v>20.5</v>
@@ -4364,31 +4431,31 @@
         <v>4.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.7</v>
+        <v>104.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH22" t="n">
         <v>18</v>
@@ -4397,10 +4464,10 @@
         <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL22" t="n">
         <v>1</v>
@@ -4412,7 +4479,7 @@
         <v>4</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>3</v>
@@ -4427,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4436,13 +4503,13 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX22" t="n">
         <v>25</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -4483,58 +4550,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="n">
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
         <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="O23" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P23" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="n">
         <v>0.705</v>
       </c>
       <c r="R23" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S23" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V23" t="n">
         <v>14.7</v>
@@ -4555,7 +4622,7 @@
         <v>21</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
         <v>0.6</v>
@@ -4564,7 +4631,7 @@
         <v>4</v>
       </c>
       <c r="AE23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4594,10 +4661,10 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4609,7 +4676,7 @@
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
         <v>24</v>
@@ -4618,7 +4685,7 @@
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="n">
         <v>13</v>
@@ -4630,10 +4697,10 @@
         <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.681</v>
+        <v>0.676</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,28 +4750,28 @@
         <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="L24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N24" t="n">
         <v>0.391</v>
       </c>
       <c r="O24" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="P24" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.784</v>
+        <v>0.78</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
@@ -4716,7 +4783,7 @@
         <v>41.2</v>
       </c>
       <c r="U24" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="V24" t="n">
         <v>14.4</v>
@@ -4734,28 +4801,28 @@
         <v>19.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.2</v>
+        <v>110</v>
       </c>
       <c r="AC24" t="n">
         <v>5.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
         <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4776,19 +4843,19 @@
         <v>2</v>
       </c>
       <c r="AO24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
         <v>23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
@@ -4797,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -4806,13 +4873,13 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ24" t="n">
         <v>8</v>
       </c>
       <c r="BA24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -4847,82 +4914,82 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
         <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.529</v>
+        <v>0.522</v>
       </c>
       <c r="H25" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I25" t="n">
         <v>35.8</v>
       </c>
       <c r="J25" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L25" t="n">
         <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
       <c r="O25" t="n">
         <v>17.8</v>
       </c>
       <c r="P25" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R25" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S25" t="n">
         <v>29.6</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="U25" t="n">
         <v>21.1</v>
       </c>
       <c r="V25" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W25" t="n">
         <v>5.6</v>
       </c>
       <c r="X25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y25" t="n">
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
         <v>4</v>
@@ -4946,7 +5013,7 @@
         <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>22</v>
@@ -4964,22 +5031,22 @@
         <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
@@ -4988,7 +5055,7 @@
         <v>21</v>
       </c>
       <c r="AY25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E26" t="n">
         <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.449</v>
+        <v>0.456</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>80</v>
+        <v>79.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.46</v>
@@ -5056,13 +5123,13 @@
         <v>6.2</v>
       </c>
       <c r="M26" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N26" t="n">
         <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="P26" t="n">
         <v>27.8</v>
@@ -5074,19 +5141,19 @@
         <v>10.4</v>
       </c>
       <c r="S26" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T26" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U26" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V26" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W26" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X26" t="n">
         <v>4.2</v>
@@ -5098,16 +5165,16 @@
         <v>22.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>101.8</v>
+        <v>101.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5122,13 +5189,13 @@
         <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
         <v>17</v>
@@ -5137,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5149,10 +5216,10 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT26" t="n">
         <v>26</v>
@@ -5182,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF27" t="n">
         <v>7</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>6</v>
       </c>
       <c r="AG27" t="n">
         <v>7</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5313,7 +5380,7 @@
         <v>14</v>
       </c>
       <c r="AL27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM27" t="n">
         <v>8</v>
@@ -5334,13 +5401,13 @@
         <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
         <v>21</v>
       </c>
       <c r="AU27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5364,7 +5431,7 @@
         <v>25</v>
       </c>
       <c r="BC27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G28" t="n">
-        <v>0.229</v>
+        <v>0.232</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,10 +5478,10 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L28" t="n">
         <v>4</v>
@@ -5426,13 +5493,13 @@
         <v>0.338</v>
       </c>
       <c r="O28" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P28" t="n">
         <v>23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
         <v>11.9</v>
@@ -5441,16 +5508,16 @@
         <v>32.7</v>
       </c>
       <c r="T28" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U28" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V28" t="n">
         <v>16.6</v>
       </c>
       <c r="W28" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
@@ -5459,10 +5526,10 @@
         <v>5.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
         <v>97.7</v>
@@ -5504,13 +5571,13 @@
         <v>27</v>
       </c>
       <c r="AO28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
         <v>25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>10</v>
@@ -5522,22 +5589,22 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
       </c>
       <c r="AW28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
@@ -5665,7 +5732,7 @@
         <v>16</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5689,7 +5756,7 @@
         <v>27</v>
       </c>
       <c r="AP29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5704,13 +5771,13 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F30" t="n">
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>0.648</v>
+        <v>0.643</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,7 +5842,7 @@
         <v>39.8</v>
       </c>
       <c r="J30" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K30" t="n">
         <v>0.496</v>
@@ -5784,28 +5851,28 @@
         <v>4.7</v>
       </c>
       <c r="M30" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
       <c r="O30" t="n">
         <v>21.8</v>
       </c>
       <c r="P30" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R30" t="n">
         <v>11.3</v>
       </c>
       <c r="S30" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U30" t="n">
         <v>26.3</v>
@@ -5814,7 +5881,7 @@
         <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
@@ -5829,22 +5896,22 @@
         <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
       </c>
       <c r="AG30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6032,7 +6099,7 @@
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6062,7 +6129,7 @@
         <v>7</v>
       </c>
       <c r="AS31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-22-2007-08</t>
+          <t>2008-03-22</t>
         </is>
       </c>
     </row>
